--- a/创业板50-创业板指-创业200-创业板综_夏普比率.xlsx
+++ b/创业板50-创业板指-创业200-创业板综_夏普比率.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
   <si>
     <t>指数代码</t>
   </si>
@@ -56,13 +56,25 @@
     <t>本年夏普比率</t>
   </si>
   <si>
+    <t>创业板50指数</t>
+  </si>
+  <si>
     <t>创业板50</t>
+  </si>
+  <si>
+    <t>创业板指数</t>
   </si>
   <si>
     <t>创业板指</t>
   </si>
   <si>
+    <t>创业板中盘200指数</t>
+  </si>
+  <si>
     <t>创业200</t>
+  </si>
+  <si>
+    <t>创业板综合指数</t>
   </si>
   <si>
     <t>创业板综</t>
@@ -695,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -714,20 +726,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1265,325 +1283,315 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.24778761061947" style="8" customWidth="1"/>
-    <col min="2" max="3" width="13.4336283185841" style="8" customWidth="1"/>
-    <col min="4" max="4" width="5.53097345132743" style="8" customWidth="1"/>
-    <col min="5" max="7" width="11.3097345132743" style="8" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="9" customWidth="1"/>
+    <col min="1" max="1" width="9.24778761061947" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13.5752212389381" style="11" customWidth="1"/>
+    <col min="3" max="3" width="13.4336283185841" style="11" customWidth="1"/>
+    <col min="4" max="4" width="5.53097345132743" style="11" customWidth="1"/>
+    <col min="5" max="7" width="11.3097345132743" style="11" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="10">
+      <c r="A2" s="11">
         <v>399673</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8">
+      <c r="C2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
         <v>2011</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <v>-0.3589</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>0.2831</v>
       </c>
-      <c r="G2" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H2" s="9">
+      <c r="G2" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H2" s="12">
         <f t="shared" ref="H2:H16" si="0">(E2-G2)/F2</f>
         <v>-1.37371953373366</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="10"/>
-      <c r="D3" s="8">
+      <c r="D3" s="11">
         <v>2012</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <v>-0.0752</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="8">
         <v>0.2932</v>
       </c>
-      <c r="G3" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H3" s="9">
+      <c r="G3" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H3" s="12">
         <f t="shared" si="0"/>
         <v>-0.358799454297408</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="D4" s="8">
+      <c r="D4" s="11">
         <v>2013</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>0.964</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>0.3401</v>
       </c>
-      <c r="G4" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="9">
+      <c r="G4" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="12">
         <f t="shared" si="0"/>
         <v>2.74625110261688</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="10"/>
-      <c r="D5" s="8">
+      <c r="D5" s="11">
         <v>2014</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <v>0.0957</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>0.2633</v>
       </c>
-      <c r="G5" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H5" s="9">
+      <c r="G5" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H5" s="12">
         <f t="shared" si="0"/>
         <v>0.249525256361565</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="D6" s="8">
+      <c r="D6" s="11">
         <v>2015</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <v>0.8443</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>0.5338</v>
       </c>
-      <c r="G6" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="G6" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H6" s="12">
         <f t="shared" si="0"/>
         <v>1.52547770700637</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
         <v>2016</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <v>-0.3162</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>0.3426</v>
       </c>
-      <c r="G7" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H7" s="9">
+      <c r="G7" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="12">
         <f t="shared" si="0"/>
         <v>-1.01050788091068</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="10"/>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
         <v>2017</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <v>-0.1439</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>0.1903</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H8" s="9">
+      <c r="G8" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H8" s="12">
         <f t="shared" si="0"/>
         <v>-0.91382028376248</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="10"/>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <v>2018</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <v>-0.3409</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>0.3173</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="G9" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H9" s="12">
         <f t="shared" si="0"/>
         <v>-1.16892530728018</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="10"/>
-      <c r="D10" s="8">
+      <c r="D10" s="11">
         <v>2019</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>0.5093</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>0.2746</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="G10" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H10" s="12">
         <f t="shared" si="0"/>
         <v>1.74544792425346</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="10"/>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <v>2020</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <v>0.8874</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>0.334</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H11" s="9">
+      <c r="G11" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="12">
         <f t="shared" si="0"/>
         <v>2.56706586826347</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="10"/>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <v>2021</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <v>0.1688</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>0.3085</v>
       </c>
-      <c r="G12" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="G12" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="12">
         <f t="shared" si="0"/>
         <v>0.449918962722852</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="10"/>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <v>2022</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <v>-0.2983</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <v>0.3064</v>
       </c>
-      <c r="G13" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="G13" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H13" s="12">
         <f t="shared" si="0"/>
         <v>-1.07147519582245</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="10"/>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <v>2023</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <v>-0.24</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <v>0.198</v>
       </c>
-      <c r="G14" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="G14" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H14" s="12">
         <f t="shared" si="0"/>
         <v>-1.36363636363636</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="10"/>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <v>2024</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <v>0.2107</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>0.4027</v>
       </c>
-      <c r="G15" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="G15" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H15" s="12">
         <f t="shared" si="0"/>
         <v>0.448721132356593</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="10"/>
-      <c r="D16" s="8">
+      <c r="D16" s="11">
         <v>2025</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <v>0.5745</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>0.321</v>
       </c>
-      <c r="G16" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="G16" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="12">
         <f t="shared" si="0"/>
         <v>1.69626168224299</v>
       </c>
@@ -1606,11 +1614,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.8318584070796" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.4336283185841" style="2" customWidth="1"/>
+    <col min="2" max="3" width="13.4336283185841" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="2" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1641,320 +1648,322 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="5">
+      <c r="A2" s="10">
         <v>399006</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>9</v>
+      <c r="B2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="2">
         <v>2011</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>-0.3588</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>0.2754</v>
       </c>
-      <c r="G2" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="G2" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H2" s="9">
         <f t="shared" ref="H2:H16" si="0">(E2-G2)/F2</f>
         <v>-1.41176470588235</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="2">
         <v>2012</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>-0.0214</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>0.2806</v>
       </c>
-      <c r="G3" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H3" s="9">
         <f t="shared" si="0"/>
         <v>-0.183178902352103</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="2">
         <v>2013</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>0.8273</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>0.3173</v>
       </c>
-      <c r="G4" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="G4" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="9">
         <f t="shared" si="0"/>
         <v>2.51276394579263</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="2">
         <v>2014</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>0.1283</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>0.2517</v>
       </c>
-      <c r="G5" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="G5" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H5" s="9">
         <f t="shared" si="0"/>
         <v>0.390544298768375</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="2">
         <v>2015</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>0.8441</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>0.5104</v>
       </c>
-      <c r="G6" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="G6" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H6" s="9">
         <f t="shared" si="0"/>
         <v>1.59502351097179</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="2">
         <v>2016</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>-0.2771</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>0.3338</v>
       </c>
-      <c r="G7" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="G7" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="9">
         <f t="shared" si="0"/>
         <v>-0.920011983223487</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="2">
         <v>2017</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>-0.1067</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0.1664</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H8" s="9">
         <f t="shared" si="0"/>
         <v>-0.821514423076923</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="2">
         <v>2018</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>-0.2865</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>0.2805</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
         <v>-1.1283422459893</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
       <c r="D10" s="2">
         <v>2019</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>0.4379</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>0.2607</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H10" s="9">
         <f t="shared" si="0"/>
         <v>1.56463367855773</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="2">
         <v>2020</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>0.6496</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>0.3127</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="G11" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="9">
         <f t="shared" si="0"/>
         <v>1.98145187080269</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="2">
         <v>2021</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>0.1202</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>0.2762</v>
       </c>
-      <c r="G12" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G12" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="9">
         <f t="shared" si="0"/>
         <v>0.326574945691528</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="2">
         <v>2022</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>-0.2937</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>0.2815</v>
       </c>
-      <c r="G13" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="G13" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H13" s="9">
         <f t="shared" si="0"/>
         <v>-1.14991119005329</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>-0.1941</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>0.1775</v>
       </c>
-      <c r="G14" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H14" s="9">
         <f t="shared" si="0"/>
         <v>-1.26253521126761</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
       <c r="D15" s="2">
         <v>2024</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>0.1323</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>0.386</v>
       </c>
-      <c r="G15" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="G15" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H15" s="9">
         <f t="shared" si="0"/>
         <v>0.265025906735751</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="2">
         <v>2025</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>0.4957</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>0.2947</v>
       </c>
-      <c r="G16" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="G16" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H16" s="9">
         <f t="shared" si="0"/>
         <v>1.58025110281642</v>
       </c>
@@ -1967,7 +1976,7 @@
       <c r="E5097" s="2"/>
       <c r="F5097" s="2"/>
       <c r="G5097" s="2"/>
-      <c r="H5097" s="3"/>
+      <c r="H5097" s="9"/>
     </row>
     <row r="5098" s="1" customFormat="1" spans="1:8">
       <c r="A5098" s="2"/>
@@ -1977,7 +1986,7 @@
       <c r="E5098" s="2"/>
       <c r="F5098" s="2"/>
       <c r="G5098" s="2"/>
-      <c r="H5098" s="3"/>
+      <c r="H5098" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1997,11 +2006,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.646017699115" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.9646017699115" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.4336283185841" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="2" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="9" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2032,278 +2041,280 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="5">
+      <c r="A2" s="10">
         <v>399019</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
+      <c r="B2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="2">
         <v>2013</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>0.6097</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>0.3245</v>
       </c>
-      <c r="G2" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="G2" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H2" s="9">
         <f t="shared" ref="H2:H14" si="0">(E2-G2)/F2</f>
         <v>1.7864406779661</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
       <c r="D3" s="2">
         <v>2014</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>0.43</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>0.2715</v>
       </c>
-      <c r="G3" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H3" s="9">
         <f t="shared" si="0"/>
         <v>1.47329650092081</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="2">
         <v>2015</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>1.2877</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>0.4819</v>
       </c>
-      <c r="G4" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="G4" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H4" s="9">
         <f t="shared" si="0"/>
         <v>2.60987756796016</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
       <c r="D5" s="2">
         <v>2016</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>-0.2257</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>0.3645</v>
       </c>
-      <c r="G5" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H5" s="3">
+      <c r="G5" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H5" s="9">
         <f t="shared" si="0"/>
         <v>-0.701508916323731</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="2">
         <v>2017</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>-0.2211</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>0.203</v>
       </c>
-      <c r="G6" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H6" s="3">
+      <c r="G6" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H6" s="9">
         <f t="shared" si="0"/>
         <v>-1.23694581280788</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="2">
         <v>2018</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>-0.347</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>0.2917</v>
       </c>
-      <c r="G7" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="G7" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H7" s="9">
         <f t="shared" si="0"/>
         <v>-1.29242372300309</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="2">
         <v>2019</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>0.3284</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0.2922</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H8" s="9">
         <f t="shared" si="0"/>
         <v>1.02121834360027</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
       <c r="D9" s="2">
         <v>2020</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>0.1737</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>0.3461</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
         <v>0.415197919676394</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
       <c r="D10" s="2">
         <v>2021</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>0.2807</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>0.2328</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="G10" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H10" s="9">
         <f t="shared" si="0"/>
         <v>1.07689003436426</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
       <c r="D11" s="2">
         <v>2022</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>-0.253</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>0.2872</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="G11" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H11" s="9">
         <f t="shared" si="0"/>
         <v>-0.985376044568245</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="2">
         <v>2023</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>0.0552</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>0.221</v>
       </c>
-      <c r="G12" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G12" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="9">
         <f t="shared" si="0"/>
         <v>0.114027149321267</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="2">
         <v>2024</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>0.0974</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>0.4508</v>
       </c>
-      <c r="G13" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="G13" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H13" s="9">
         <f t="shared" si="0"/>
         <v>0.149511978704525</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
       <c r="D14" s="2">
         <v>2025</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>0.2916</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>0.318</v>
       </c>
-      <c r="G14" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="H14" s="9">
         <f t="shared" si="0"/>
         <v>0.822641509433962</v>
       </c>
@@ -2316,7 +2327,7 @@
       <c r="E5095" s="2"/>
       <c r="F5095" s="2"/>
       <c r="G5095" s="2"/>
-      <c r="H5095" s="3"/>
+      <c r="H5095" s="9"/>
     </row>
     <row r="5096" s="1" customFormat="1" spans="1:8">
       <c r="A5096" s="2"/>
@@ -2326,7 +2337,7 @@
       <c r="E5096" s="2"/>
       <c r="F5096" s="2"/>
       <c r="G5096" s="2"/>
-      <c r="H5096" s="3"/>
+      <c r="H5096" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2346,7 +2357,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.24778761061947" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.646017699115" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.6283185840708" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.4336283185841" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="2" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="2" customWidth="1"/>
@@ -2384,20 +2395,22 @@
       <c r="A2" s="5">
         <v>399102</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="2">
         <v>2011</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <v>-0.3542</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>0.2739</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>0.03</v>
       </c>
       <c r="H2" s="4">
@@ -2407,18 +2420,18 @@
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="5"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="5"/>
       <c r="D3" s="2">
         <v>2012</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>-0.0191</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="7">
         <v>0.2884</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>0.03</v>
       </c>
       <c r="H3" s="4">
@@ -2428,18 +2441,18 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="5"/>
-      <c r="B4" s="2"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="5"/>
       <c r="D4" s="2">
         <v>2013</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>0.7473</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>0.3121</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>0.03</v>
       </c>
       <c r="H4" s="4">
@@ -2449,18 +2462,18 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="2">
         <v>2014</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>0.2704</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <v>0.2538</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>0.03</v>
       </c>
       <c r="H5" s="4">
@@ -2470,18 +2483,18 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
       <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="5"/>
       <c r="D6" s="2">
         <v>2015</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>1.0661</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>0.4935</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>0.03</v>
       </c>
       <c r="H6" s="4">
@@ -2491,18 +2504,18 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
       <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="5"/>
       <c r="D7" s="2">
         <v>2016</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>-0.2035</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>0.3445</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>0.03</v>
       </c>
       <c r="H7" s="4">
@@ -2512,18 +2525,18 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
       <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="5"/>
       <c r="D8" s="2">
         <v>2017</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>-0.1532</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>0.1826</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>0.03</v>
       </c>
       <c r="H8" s="4">
@@ -2533,18 +2546,18 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
       <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="5"/>
       <c r="D9" s="2">
         <v>2018</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>-0.3112</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <v>0.2813</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>0.03</v>
       </c>
       <c r="H9" s="4">
@@ -2554,18 +2567,18 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
       <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="5"/>
       <c r="D10" s="2">
         <v>2019</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>0.3872</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>0.2655</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>0.03</v>
       </c>
       <c r="H10" s="4">
@@ -2575,18 +2588,18 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
       <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="5"/>
       <c r="D11" s="2">
         <v>2020</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>0.4785</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="7">
         <v>0.3099</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>0.03</v>
       </c>
       <c r="H11" s="4">
@@ -2596,18 +2609,18 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
       <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="B12" s="6"/>
       <c r="C12" s="5"/>
       <c r="D12" s="2">
         <v>2021</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>0.1793</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="7">
         <v>0.2269</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>0.03</v>
       </c>
       <c r="H12" s="4">
@@ -2617,18 +2630,18 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
       <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="5"/>
       <c r="D13" s="2">
         <v>2022</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>-0.2677</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>0.2678</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>0.03</v>
       </c>
       <c r="H13" s="4">
@@ -2638,18 +2651,18 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
       <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="5"/>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>-0.0541</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>0.1687</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <v>0.03</v>
       </c>
       <c r="H14" s="4">
@@ -2659,18 +2672,18 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
       <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="5"/>
       <c r="D15" s="2">
         <v>2024</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>0.0963</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>0.3935</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <v>0.03</v>
       </c>
       <c r="H15" s="4">
@@ -2680,18 +2693,18 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
       <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="5"/>
       <c r="D16" s="2">
         <v>2025</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>0.404</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>0.2842</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>0.03</v>
       </c>
       <c r="H16" s="4">
@@ -2700,31 +2713,31 @@
       </c>
     </row>
     <row r="17" spans="7:7">
-      <c r="G17" s="7"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" spans="7:7">
-      <c r="G18" s="7"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" spans="7:7">
-      <c r="G19" s="7"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" spans="7:7">
-      <c r="G20" s="7"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" spans="7:7">
-      <c r="G21" s="7"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="7:7">
-      <c r="G22" s="7"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="7:7">
-      <c r="G23" s="7"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="7:7">
-      <c r="G24" s="7"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" spans="7:7">
-      <c r="G25" s="7"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="2914" s="1" customFormat="1" spans="1:8">
       <c r="A2914" s="2"/>
@@ -2749,7 +2762,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A16"/>
-    <mergeCell ref="B5:B16"/>
+    <mergeCell ref="B2:B16"/>
     <mergeCell ref="C2:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/创业板50-创业板指-创业200-创业板综_夏普比率.xlsx
+++ b/创业板50-创业板指-创业200-创业板综_夏普比率.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20152" windowHeight="8955" activeTab="3"/>
+    <workbookView windowWidth="20752" windowHeight="9555" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="创业板50" sheetId="1" r:id="rId1"/>
@@ -707,7 +707,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -733,9 +733,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1283,51 +1280,51 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.24778761061947" style="11" customWidth="1"/>
-    <col min="2" max="2" width="13.5752212389381" style="11" customWidth="1"/>
-    <col min="3" max="3" width="13.4336283185841" style="11" customWidth="1"/>
-    <col min="4" max="4" width="5.53097345132743" style="11" customWidth="1"/>
-    <col min="5" max="7" width="11.3097345132743" style="11" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="12" customWidth="1"/>
+    <col min="1" max="1" width="9.24778761061947" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.5752212389381" style="10" customWidth="1"/>
+    <col min="3" max="3" width="13.4336283185841" style="10" customWidth="1"/>
+    <col min="4" max="4" width="5.53097345132743" style="10" customWidth="1"/>
+    <col min="5" max="7" width="11.3097345132743" style="10" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>399673</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>2011</v>
       </c>
       <c r="E2" s="8">
@@ -1339,13 +1336,13 @@
       <c r="G2" s="8">
         <v>0.03</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <f t="shared" ref="H2:H16" si="0">(E2-G2)/F2</f>
         <v>-1.37371953373366</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>2012</v>
       </c>
       <c r="E3" s="8">
@@ -1357,13 +1354,13 @@
       <c r="G3" s="8">
         <v>0.03</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <f t="shared" si="0"/>
         <v>-0.358799454297408</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>2013</v>
       </c>
       <c r="E4" s="8">
@@ -1375,13 +1372,13 @@
       <c r="G4" s="8">
         <v>0.03</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <f t="shared" si="0"/>
         <v>2.74625110261688</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>2014</v>
       </c>
       <c r="E5" s="8">
@@ -1393,13 +1390,13 @@
       <c r="G5" s="8">
         <v>0.03</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>0.249525256361565</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>2015</v>
       </c>
       <c r="E6" s="8">
@@ -1411,13 +1408,13 @@
       <c r="G6" s="8">
         <v>0.03</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <f t="shared" si="0"/>
         <v>1.52547770700637</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>2016</v>
       </c>
       <c r="E7" s="8">
@@ -1429,13 +1426,13 @@
       <c r="G7" s="8">
         <v>0.03</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>-1.01050788091068</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>2017</v>
       </c>
       <c r="E8" s="8">
@@ -1447,13 +1444,13 @@
       <c r="G8" s="8">
         <v>0.03</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>-0.91382028376248</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>2018</v>
       </c>
       <c r="E9" s="8">
@@ -1465,13 +1462,13 @@
       <c r="G9" s="8">
         <v>0.03</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>-1.16892530728018</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>2019</v>
       </c>
       <c r="E10" s="8">
@@ -1483,13 +1480,13 @@
       <c r="G10" s="8">
         <v>0.03</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <f t="shared" si="0"/>
         <v>1.74544792425346</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>2020</v>
       </c>
       <c r="E11" s="8">
@@ -1501,13 +1498,13 @@
       <c r="G11" s="8">
         <v>0.03</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
         <v>2.56706586826347</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>2021</v>
       </c>
       <c r="E12" s="8">
@@ -1519,13 +1516,13 @@
       <c r="G12" s="8">
         <v>0.03</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <f t="shared" si="0"/>
         <v>0.449918962722852</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>2022</v>
       </c>
       <c r="E13" s="8">
@@ -1537,13 +1534,13 @@
       <c r="G13" s="8">
         <v>0.03</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>-1.07147519582245</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <v>2023</v>
       </c>
       <c r="E14" s="8">
@@ -1555,13 +1552,13 @@
       <c r="G14" s="8">
         <v>0.03</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f t="shared" si="0"/>
         <v>-1.36363636363636</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>2024</v>
       </c>
       <c r="E15" s="8">
@@ -1573,13 +1570,13 @@
       <c r="G15" s="8">
         <v>0.03</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <f t="shared" si="0"/>
         <v>0.448721132356593</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <v>2025</v>
       </c>
       <c r="E16" s="8">
@@ -1591,7 +1588,7 @@
       <c r="G16" s="8">
         <v>0.03</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f t="shared" si="0"/>
         <v>1.69626168224299</v>
       </c>
@@ -1617,7 +1614,7 @@
     <col min="2" max="3" width="13.4336283185841" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="2" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="9" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1648,13 +1645,13 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>399006</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="2">
@@ -1669,15 +1666,15 @@
       <c r="G2" s="8">
         <v>0.03</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="4">
         <f t="shared" ref="H2:H16" si="0">(E2-G2)/F2</f>
         <v>-1.41176470588235</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="2">
         <v>2012</v>
       </c>
@@ -1690,15 +1687,15 @@
       <c r="G3" s="8">
         <v>0.03</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="4">
         <f t="shared" si="0"/>
         <v>-0.183178902352103</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="2">
         <v>2013</v>
       </c>
@@ -1711,15 +1708,15 @@
       <c r="G4" s="8">
         <v>0.03</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="4">
         <f t="shared" si="0"/>
         <v>2.51276394579263</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="2">
         <v>2014</v>
       </c>
@@ -1732,15 +1729,15 @@
       <c r="G5" s="8">
         <v>0.03</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="4">
         <f t="shared" si="0"/>
         <v>0.390544298768375</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="2">
         <v>2015</v>
       </c>
@@ -1753,15 +1750,15 @@
       <c r="G6" s="8">
         <v>0.03</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="4">
         <f t="shared" si="0"/>
         <v>1.59502351097179</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="2">
         <v>2016</v>
       </c>
@@ -1774,15 +1771,15 @@
       <c r="G7" s="8">
         <v>0.03</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="4">
         <f t="shared" si="0"/>
         <v>-0.920011983223487</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2">
         <v>2017</v>
       </c>
@@ -1795,15 +1792,15 @@
       <c r="G8" s="8">
         <v>0.03</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>-0.821514423076923</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="2">
         <v>2018</v>
       </c>
@@ -1816,15 +1813,15 @@
       <c r="G9" s="8">
         <v>0.03</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="4">
         <f t="shared" si="0"/>
         <v>-1.1283422459893</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="2">
         <v>2019</v>
       </c>
@@ -1837,15 +1834,15 @@
       <c r="G10" s="8">
         <v>0.03</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="4">
         <f t="shared" si="0"/>
         <v>1.56463367855773</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="2">
         <v>2020</v>
       </c>
@@ -1858,15 +1855,15 @@
       <c r="G11" s="8">
         <v>0.03</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <f t="shared" si="0"/>
         <v>1.98145187080269</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="2">
         <v>2021</v>
       </c>
@@ -1879,15 +1876,15 @@
       <c r="G12" s="8">
         <v>0.03</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="4">
         <f t="shared" si="0"/>
         <v>0.326574945691528</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="2">
         <v>2022</v>
       </c>
@@ -1900,15 +1897,15 @@
       <c r="G13" s="8">
         <v>0.03</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="4">
         <f t="shared" si="0"/>
         <v>-1.14991119005329</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
@@ -1921,15 +1918,15 @@
       <c r="G14" s="8">
         <v>0.03</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="4">
         <f t="shared" si="0"/>
         <v>-1.26253521126761</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="2">
         <v>2024</v>
       </c>
@@ -1942,15 +1939,15 @@
       <c r="G15" s="8">
         <v>0.03</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="4">
         <f t="shared" si="0"/>
         <v>0.265025906735751</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="2">
         <v>2025</v>
       </c>
@@ -1963,7 +1960,7 @@
       <c r="G16" s="8">
         <v>0.03</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="4">
         <f t="shared" si="0"/>
         <v>1.58025110281642</v>
       </c>
@@ -1976,7 +1973,7 @@
       <c r="E5097" s="2"/>
       <c r="F5097" s="2"/>
       <c r="G5097" s="2"/>
-      <c r="H5097" s="9"/>
+      <c r="H5097" s="4"/>
     </row>
     <row r="5098" s="1" customFormat="1" spans="1:8">
       <c r="A5098" s="2"/>
@@ -1986,7 +1983,7 @@
       <c r="E5098" s="2"/>
       <c r="F5098" s="2"/>
       <c r="G5098" s="2"/>
-      <c r="H5098" s="9"/>
+      <c r="H5098" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2010,7 +2007,7 @@
     <col min="3" max="3" width="13.4336283185841" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.53097345132743" style="2" customWidth="1"/>
     <col min="5" max="7" width="11.3097345132743" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.4336283185841" style="9" customWidth="1"/>
+    <col min="8" max="8" width="13.4336283185841" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2041,13 +2038,13 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>399019</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="2">
@@ -2062,15 +2059,15 @@
       <c r="G2" s="8">
         <v>0.03</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="4">
         <f t="shared" ref="H2:H14" si="0">(E2-G2)/F2</f>
         <v>1.7864406779661</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
       <c r="D3" s="2">
         <v>2014</v>
       </c>
@@ -2083,15 +2080,15 @@
       <c r="G3" s="8">
         <v>0.03</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="4">
         <f t="shared" si="0"/>
         <v>1.47329650092081</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="2">
         <v>2015</v>
       </c>
@@ -2104,15 +2101,15 @@
       <c r="G4" s="8">
         <v>0.03</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="4">
         <f t="shared" si="0"/>
         <v>2.60987756796016</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="2">
         <v>2016</v>
       </c>
@@ -2125,15 +2122,15 @@
       <c r="G5" s="8">
         <v>0.03</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="4">
         <f t="shared" si="0"/>
         <v>-0.701508916323731</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="2">
         <v>2017</v>
       </c>
@@ -2146,15 +2143,15 @@
       <c r="G6" s="8">
         <v>0.03</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="4">
         <f t="shared" si="0"/>
         <v>-1.23694581280788</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="2">
         <v>2018</v>
       </c>
@@ -2167,15 +2164,15 @@
       <c r="G7" s="8">
         <v>0.03</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="4">
         <f t="shared" si="0"/>
         <v>-1.29242372300309</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2">
         <v>2019</v>
       </c>
@@ -2188,15 +2185,15 @@
       <c r="G8" s="8">
         <v>0.03</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="4">
         <f t="shared" si="0"/>
         <v>1.02121834360027</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="2">
         <v>2020</v>
       </c>
@@ -2209,15 +2206,15 @@
       <c r="G9" s="8">
         <v>0.03</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="4">
         <f t="shared" si="0"/>
         <v>0.415197919676394</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="2">
         <v>2021</v>
       </c>
@@ -2230,15 +2227,15 @@
       <c r="G10" s="8">
         <v>0.03</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="4">
         <f t="shared" si="0"/>
         <v>1.07689003436426</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="2">
         <v>2022</v>
       </c>
@@ -2251,15 +2248,15 @@
       <c r="G11" s="8">
         <v>0.03</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <f t="shared" si="0"/>
         <v>-0.985376044568245</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="2">
         <v>2023</v>
       </c>
@@ -2272,15 +2269,15 @@
       <c r="G12" s="8">
         <v>0.03</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="4">
         <f t="shared" si="0"/>
         <v>0.114027149321267</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="2">
         <v>2024</v>
       </c>
@@ -2293,15 +2290,15 @@
       <c r="G13" s="8">
         <v>0.03</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="4">
         <f t="shared" si="0"/>
         <v>0.149511978704525</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="2">
         <v>2025</v>
       </c>
@@ -2314,7 +2311,7 @@
       <c r="G14" s="8">
         <v>0.03</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="4">
         <f t="shared" si="0"/>
         <v>0.822641509433962</v>
       </c>
@@ -2327,7 +2324,7 @@
       <c r="E5095" s="2"/>
       <c r="F5095" s="2"/>
       <c r="G5095" s="2"/>
-      <c r="H5095" s="9"/>
+      <c r="H5095" s="4"/>
     </row>
     <row r="5096" s="1" customFormat="1" spans="1:8">
       <c r="A5096" s="2"/>
@@ -2337,7 +2334,7 @@
       <c r="E5096" s="2"/>
       <c r="F5096" s="2"/>
       <c r="G5096" s="2"/>
-      <c r="H5096" s="9"/>
+      <c r="H5096" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
